--- a/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-documentreference.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-documentreference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-10T07:10:15+00:00</t>
+    <t>2026-01-28T12:36:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,7 +689,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|Practitioner|Group|Device)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|Group|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device)
 </t>
   </si>
   <si>
@@ -755,7 +755,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -789,7 +789,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -823,7 +823,7 @@
     <t>DocumentReference.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -942,7 +942,7 @@
     <t>DocumentReference.relatesTo.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference)
 </t>
   </si>
   <si>
@@ -1627,7 +1627,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.03125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
